--- a/modules/report_hub/docs/templates/Report_Hub_Config_Template.xlsx
+++ b/modules/report_hub/docs/templates/Report_Hub_Config_Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Reports" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CrossRef" sheetId="3" state="visible" r:id="rId3"/>
-  </sheets>
-</workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15 xr xr6 xr10 xr2">
+  <ns0:workbookPr date1904="false"/>
+  <ns0:bookViews>
+    <ns0:workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+  </ns0:bookViews>
+  <ns0:sheets>
+    <ns0:sheet name="Settings" sheetId="1" state="visible" ns2:id="rId1"/>
+    <ns0:sheet name="Reports" sheetId="2" state="visible" ns2:id="rId2"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1266,239 +1265,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="30.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="45.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
 </file>
--- a/modules/report_hub/docs/templates/Report_Hub_Config_Template.xlsx
+++ b/modules/report_hub/docs/templates/Report_Hub_Config_Template.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15 xr xr6 xr10 xr2">
-  <ns0:workbookPr date1904="false"/>
-  <ns0:bookViews>
-    <ns0:workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
-  </ns0:bookViews>
-  <ns0:sheets>
-    <ns0:sheet name="Settings" sheetId="1" state="visible" ns2:id="rId1"/>
-    <ns0:sheet name="Reports" sheetId="2" state="visible" ns2:id="rId2"/>
-  </ns0:sheets>
-</ns0:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Reports" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>

--- a/modules/report_hub/docs/templates/Report_Hub_Config_Template.xlsx
+++ b/modules/report_hub/docs/templates/Report_Hub_Config_Template.xlsx
@@ -1,284 +1,241 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Documents/Turas/modules/report_hub/docs/templates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F1CB521-76E3-C542-AB44-8B18D0668623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="21140" windowHeight="13180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Reports" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Settings" sheetId="1" r:id="rId1"/>
+    <sheet name="Reports" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
-  <si>
-    <t xml:space="preserve">Report Hub Configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings for combining multiple Turas HTML reports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legend:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your Input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read Only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid Values / Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROJECT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">project_title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combined Brand Study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQUIRED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main title displayed in the combined report header</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any descriptive text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subtitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional subtitle displayed below the main title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any text or leave blank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">company_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Research LampPost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company name shown in the 'Prepared by' line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your company or research firm name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">client_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client name shown as 'Prepared for' (optional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client name or leave blank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRANDING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brand_colour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#323367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary brand colour for report header and accents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hex colour code (e.g., #323367)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accent_colour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#CC9900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secondary accent colour for highlights and tabs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hex colour code (e.g., #CC9900)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logo_path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Path to logo image (PNG, JPG, or SVG). Embedded as Base64 in report.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File path (relative to config or absolute)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OUTPUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">output_dir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Output directory for the combined report. Created if needed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directory path (relative to config or absolute)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">output_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Output filename. Auto-generated from title + date if blank.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filename ending in .html (e.g., Brand_Report_2026.html)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report Files</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List all HTML reports to combine (one per row, in display order)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">report_path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">report_label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">report_key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">report_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Path to the HTML report file (absolute or relative to this config file)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Display name shown in navigation tabs (e.g., 'Brand Tracker', 'Crosstabs')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Unique ID for DOM namespacing. Letters/numbers/hyphens/underscores only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Sort order for navigation tabs (1, 2, 3...)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Report type override (auto-detected if blank)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">output/Brand_Tracker_Report.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">output/Crosstabs_Report.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross-Tabulations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tabs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">output/Confidence_Report.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidence Intervals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">confidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross-Reference Mapping (Optional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map question codes between tracker and tabs reports for cross-linking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tracker_code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tabs_code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Question code in the tracker report (must match tracker's QuestionCode)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Corresponding question code in the tabs/crosstabs report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Optional notes about the mapping (for documentation only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q1_Brand_Awareness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand awareness - same question both waves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3_Satisfaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall satisfaction rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_NPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net Promoter Score</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="69">
+  <si>
+    <t>Report Hub Configuration</t>
+  </si>
+  <si>
+    <t>Settings for combining multiple Turas HTML reports</t>
+  </si>
+  <si>
+    <t>Legend:</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>Your Input</t>
+  </si>
+  <si>
+    <t>Read Only</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Required?</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Valid Values / Notes</t>
+  </si>
+  <si>
+    <t>PROJECT</t>
+  </si>
+  <si>
+    <t>project_title</t>
+  </si>
+  <si>
+    <t>Combined Brand Study</t>
+  </si>
+  <si>
+    <t>REQUIRED</t>
+  </si>
+  <si>
+    <t>Main title displayed in the combined report header</t>
+  </si>
+  <si>
+    <t>Any descriptive text</t>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Optional subtitle displayed below the main title</t>
+  </si>
+  <si>
+    <t>Any text or leave blank</t>
+  </si>
+  <si>
+    <t>company_name</t>
+  </si>
+  <si>
+    <t>The Research LampPost</t>
+  </si>
+  <si>
+    <t>Company name shown in the 'Prepared by' line</t>
+  </si>
+  <si>
+    <t>Your company or research firm name</t>
+  </si>
+  <si>
+    <t>client_name</t>
+  </si>
+  <si>
+    <t>Client name shown as 'Prepared for' (optional)</t>
+  </si>
+  <si>
+    <t>Client name or leave blank</t>
+  </si>
+  <si>
+    <t>BRANDING</t>
+  </si>
+  <si>
+    <t>brand_colour</t>
+  </si>
+  <si>
+    <t>#323367</t>
+  </si>
+  <si>
+    <t>Primary brand colour for report header and accents</t>
+  </si>
+  <si>
+    <t>Hex colour code (e.g., #323367)</t>
+  </si>
+  <si>
+    <t>accent_colour</t>
+  </si>
+  <si>
+    <t>#CC9900</t>
+  </si>
+  <si>
+    <t>Secondary accent colour for highlights and tabs</t>
+  </si>
+  <si>
+    <t>Hex colour code (e.g., #CC9900)</t>
+  </si>
+  <si>
+    <t>logo_path</t>
+  </si>
+  <si>
+    <t>Path to logo image (PNG, JPG, or SVG). Embedded as Base64 in report.</t>
+  </si>
+  <si>
+    <t>File path (relative to config or absolute)</t>
+  </si>
+  <si>
+    <t>OUTPUT</t>
+  </si>
+  <si>
+    <t>output_dir</t>
+  </si>
+  <si>
+    <t>Output directory for the combined report. Created if needed.</t>
+  </si>
+  <si>
+    <t>Directory path (relative to config or absolute)</t>
+  </si>
+  <si>
+    <t>output_file</t>
+  </si>
+  <si>
+    <t>Output filename. Auto-generated from title + date if blank.</t>
+  </si>
+  <si>
+    <t>Filename ending in .html (e.g., Brand_Report_2026.html)</t>
+  </si>
+  <si>
+    <t>Report Files</t>
+  </si>
+  <si>
+    <t>List all HTML reports to combine (one per row, in display order)</t>
+  </si>
+  <si>
+    <t>report_path</t>
+  </si>
+  <si>
+    <t>report_label</t>
+  </si>
+  <si>
+    <t>report_key</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>report_type</t>
+  </si>
+  <si>
+    <t>[REQUIRED] Path to the HTML report file (absolute or relative to this config file)</t>
+  </si>
+  <si>
+    <t>[REQUIRED] Display name shown in navigation tabs (e.g., 'Brand Tracker', 'Crosstabs')</t>
+  </si>
+  <si>
+    <t>[REQUIRED] Unique ID for DOM namespacing. Letters/numbers/hyphens/underscores only.</t>
+  </si>
+  <si>
+    <t>[REQUIRED] Sort order for navigation tabs (1, 2, 3...)</t>
+  </si>
+  <si>
+    <t>[Optional] Report type override (auto-detected if blank)</t>
+  </si>
+  <si>
+    <t>output/Brand_Tracker_Report.html</t>
+  </si>
+  <si>
+    <t>Brand Tracker</t>
+  </si>
+  <si>
+    <t>tracker</t>
+  </si>
+  <si>
+    <t>output/Crosstabs_Report.html</t>
+  </si>
+  <si>
+    <t>Cross-Tabulations</t>
+  </si>
+  <si>
+    <t>tabs</t>
+  </si>
+  <si>
+    <t>output/Confidence_Report.html</t>
+  </si>
+  <si>
+    <t>Confidence Intervals</t>
+  </si>
+  <si>
+    <t>confidence</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -287,71 +244,83 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
       <color rgb="FF323367"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF546E7A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF323367"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFD32F2F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF546E7A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF546E7A"/>
       <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF323367"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFD32F2F"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF546E7A"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF546E7A"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF388E3C"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF37474F"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -423,6 +392,7 @@
       <bottom style="thin">
         <color rgb="FFB0BEC5"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -437,19 +407,14 @@
       <bottom style="thin">
         <color rgb="FF323367"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -466,9 +431,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -491,6 +453,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -498,6 +470,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -779,238 +760,246 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="55.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="35.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="55.6640625" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="s">
+    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="11" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1023,246 +1012,245 @@
     <mergeCell ref="A15:E15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="45.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="25.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="14">
         <v>1</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="14">
         <v>2</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="14">
         <v>3</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="D5:D22">
+  <dataValidations count="2">
+    <dataValidation type="whole" showInputMessage="1" showErrorMessage="1" sqref="D5:D22" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>1</formula1>
       <formula2>99</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E22" xr:uid="{00000000-0002-0000-0100-000001000000}">
+      <formula1>"tracker,tabs"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"tracker,tabs"</xm:f>
-          </x14:formula1>
-          <xm:sqref>E5:E22</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/modules/report_hub/docs/templates/Report_Hub_Config_Template.xlsx
+++ b/modules/report_hub/docs/templates/Report_Hub_Config_Template.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Settings" sheetId="1" r:id="rId1"/>
-    <sheet name="Reports" sheetId="2" r:id="rId2"/>
-    <sheet name="Slides" sheetId="3" r:id="rId3"/>
+    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Reports" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Slides" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,8 +134,33 @@
       <color rgb="0094a3b8"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00388E3C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00546E7A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00546E7A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -192,8 +219,33 @@
         <bgColor rgb="001F2937"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F8E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECEFF1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -275,11 +327,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -342,6 +398,25 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -701,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="38.6640625" customWidth="1" style="16" min="1" max="1"/>
@@ -1087,6 +1162,132 @@
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>Markdown text or leave blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>ABOUT</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>analyst_name</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="n"/>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>Analyst name(s) displayed on the About tab</t>
+        </is>
+      </c>
+      <c r="E22" s="34" t="inlineStr">
+        <is>
+          <t>Name(s), e.g. "Duncan Brett &amp; Jess Taylor"</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>analyst_email</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>Contact email address(es) for the About tab. Separate multiple with semicolons.</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>Email(s), e.g. "a@co.za ; b@co.za"</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>analyst_phone</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="n"/>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Contact phone number displayed on the About tab</t>
+        </is>
+      </c>
+      <c r="E24" s="34" t="inlineStr">
+        <is>
+          <t>Phone number or leave blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>appendices</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="n"/>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Appendices reference text displayed on the About tab</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>Descriptive text or leave blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="n"/>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>Editable notes displayed on the About tab. Supports markdown syntax (bold, italic, headings, bullets).</t>
+        </is>
+      </c>
+      <c r="E26" s="34" t="inlineStr">
         <is>
           <t>Markdown text or leave blank</t>
         </is>
@@ -1412,7 +1613,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>

--- a/modules/report_hub/docs/templates/Report_Hub_Config_Template.xlsx
+++ b/modules/report_hub/docs/templates/Report_Hub_Config_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Documents/Turas/modules/report_hub/docs/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BEB67F-E413-DD41-A7CC-501CDA2BA856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE271590-AD5D-A04C-9EB8-1A68081DA928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26200" yWindow="1860" windowWidth="17720" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26200" yWindow="1860" windowWidth="17720" windowHeight="12480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="83">
   <si>
     <t>Report Hub Configuration</t>
   </si>
@@ -265,6 +265,12 @@
   </si>
   <si>
     <t>duncan@researchlamppost.co.za ; jess@researchlamppost.co.za</t>
+  </si>
+  <si>
+    <t>image_path</t>
+  </si>
+  <si>
+    <t>[OPTIONAL] The path and filename of the image to upload</t>
   </si>
 </sst>
 </file>
@@ -527,6 +533,12 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -535,12 +547,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -851,22 +857,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -903,13 +909,13 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -976,13 +982,13 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
@@ -1036,13 +1042,13 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
@@ -1091,7 +1097,7 @@
       <c r="A19" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="20" t="s">
         <v>80</v>
       </c>
       <c r="C19" s="13"/>
@@ -1158,22 +1164,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
@@ -1370,25 +1376,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC656C5A-2457-C246-A856-1939FC86D8E5}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
         <v>66</v>
       </c>
@@ -1398,37 +1405,47 @@
       <c r="C4" s="17" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A5" s="23" t="s">
+      <c r="D4" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A5" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="19" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5" s="19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="18"/>
       <c r="C6" s="8"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="8"/>
       <c r="B7" s="18"/>
       <c r="C7" s="8"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="8"/>
       <c r="B8" s="18"/>
       <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
